--- a/order_forms/042_ultrasound_order_form--order_forms.xlsx
+++ b/order_forms/042_ultrasound_order_form--order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>first_name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>last_name</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>date_of_visit</t>
+          <t>Date of Visit</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>time_of_visit</t>
+          <t>Time of Visit</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>medical_record_number</t>
+          <t>Medical Record Number</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>insurance_provider</t>
+          <t>Insurance Provider</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>patient_address</t>
+          <t>Patient Address</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>billing_provider</t>
+          <t>Billing Provider</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ultrasound_type</t>
+          <t>Ultrasound Type</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ultrasound_service</t>
+          <t>Ultrasound Service</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>insurance_claim</t>
+          <t>Insurance Claim</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>patient_phone</t>
+          <t>Patient Phone</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>doctor_name</t>
+          <t>Doctor's Name</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>doctor_title</t>
+          <t>Doctor's Title</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>doctor_email</t>
+          <t>Doctor's Email</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>patient_relationship</t>
+          <t>Patient Relationship</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -883,7 +883,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>patient_dob</t>
+          <t>Patient's Date of Birth</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>patient_gender</t>
+          <t>Patient's Gender</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>patient_race</t>
+          <t>Patient's Race</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -962,7 +962,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>billing_address</t>
+          <t>Billing Address</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>billing_provider_name</t>
+          <t>Billing Provider Name</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>patient_address</t>
+          <t>patient_address_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>patient_address</t>
+          <t>Patient Address 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>billing_phone</t>
+          <t>Billing Phone</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>patient_dob</t>
+          <t>patient_dob_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>patient_dob</t>
+          <t>Patient Dob 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>patient_gender</t>
+          <t>patient_gender_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>patient_gender</t>
+          <t>Patient Gender 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
